--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92566712905</v>
+        <v>46157.93093689023</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93093689023</v>
+        <v>46157.93170505612</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93170505612</v>
+        <v>46157.93398554205</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93398554205</v>
+        <v>46157.93716284772</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93716284772</v>
+        <v>46158.28214894026</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28214894026</v>
+        <v>46158.29676368357</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29676368357</v>
+        <v>46158.29812995465</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29812995465</v>
+        <v>46158.33385871604</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33385871604</v>
+        <v>46158.36855647517</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/10. ООО Газпромнефть - Региональные продажи/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36855647517</v>
+        <v>46158.37286357457</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
